--- a/ligi_soccerstats.xlsx
+++ b/ligi_soccerstats.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>URL</t>
   </si>
@@ -21,12 +21,15 @@
   <si>
     <t>https://www.soccerstats.com/results.asp?league=england&amp;pmtype=bydate</t>
   </si>
+  <si>
+    <t>https://www.soccerstats.com/results.asp?league=germany&amp;pmtype=bydate</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -37,6 +40,10 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
     </font>
     <font>
       <u/>
@@ -57,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -65,6 +72,9 @@
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -302,11 +312,17 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" location="google_vignette" ref="A2"/>
     <hyperlink r:id="rId2" location="google_vignette" ref="A3"/>
+    <hyperlink r:id="rId3" ref="A4"/>
   </hyperlinks>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>